--- a/ui_runner/graded_slate/2026-04-02/graded_wcbb_2026-04-02.xlsx
+++ b/ui_runner/graded_slate/2026-04-02/graded_wcbb_2026-04-02.xlsx
@@ -656,7 +656,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 15:43</t>
+          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 19:03</t>
         </is>
       </c>
     </row>

--- a/ui_runner/graded_slate/2026-04-02/graded_wcbb_2026-04-02.xlsx
+++ b/ui_runner/graded_slate/2026-04-02/graded_wcbb_2026-04-02.xlsx
@@ -656,7 +656,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 19:03</t>
+          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-13 21:19</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="S2" s="13" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="S4" s="13" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="T28" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="T30" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T32" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="T34" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="T36" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="T38" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="T40" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="T41" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="T42" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="T43" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T44" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="T45" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="T46" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="T48" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="T49" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="T50" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="T51" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="T52" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="T53" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="T54" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="T55" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="T56" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="T57" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="T58" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="T59" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="T60" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="T61" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="T62" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="T63" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="T64" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="T65" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="T66" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="T67" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="T68" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T69" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="T70" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="T71" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="T72" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="T73" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T74" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="T75" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="T76" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="T77" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="T78" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="T79" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="T80" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="T81" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="T82" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="T83" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="T84" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="T85" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="T86" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="T87" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="T88" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="T89" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="T90" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="T91" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="T92" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="T93" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="T94" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="T95" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="T96" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="T97" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="T98" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="T99" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="T100" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="T101" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="T102" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T103" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="T104" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="T105" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="T106" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="T107" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="T108" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="T109" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="T110" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="T111" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="T112" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="T113" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="T114" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="T115" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="T116" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="T117" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="T118" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="T119" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="T120" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="T121" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="T122" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="T123" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="T124" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="T125" s="4" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="T126" s="13" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A; NO_ACTUAL</t>
         </is>
       </c>
     </row>
